--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The case to run. A folder holding an `input_data/` with the three CSVs. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. Anything under `data_folder/` works; the path is relative to the project root. `run_model.py --list` prints the folders that qualify.</t>
+          <t>WHICH CASE THE MODEL RUNS. A folder holding an `input_data/` with the three CSV files: inputs.csv, composition.csv and TCs.csv. The path is written from the project root. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. To see which folders qualify, run:  ./.venv/bin/python 01_run_model.py --list</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which of the two engines solves the system: 'optimized' or 'LA'. SAFE TO CHANGE: yes, but know that the two disagree beyond `basic_test` -- seven documented divergences, some of which silently change results. See documentation/DEFECTS.md §2. 'optimized' is the default because it is what the project has always run; it is not the more correct of the two.</t>
+          <t>WHICH OF THE TWO ENGINES SOLVES THE SYSTEM: 'optimized' or 'LA'. SAFE TO CHANGE: yes, but read this first. The two engines disagree beyond the basic_test case -- seven documented differences, several of which change results silently (documentation/DEFECTS.md section 2). 'optimized' is the default because it is what this project has always run, NOT because it is the more correct of the two.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Draw the Sankey figures as part of a run. SAFE TO CHANGE: yes.</t>
+          <t>DRAW THE SANKEY FIGURES AS PART OF A RUN. These show how much mass goes where, in total and per element. SAFE TO CHANGE: yes. Set to False to solve without drawing anything.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Also draw the structure diagram on every run. Off by default because the structure changes only when the TC table does, while the Sankeys change with every result. SAFE TO CHANGE: yes.</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM ON EVERY RUN. This shows how the flows connect and the transfer coefficients behind each arrow. Off by default because the structure only changes when the TC table changes, while the Sankeys change with every result. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -531,106 +531,144 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>formats</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which file formats to write, from 'svg', 'png' and 'pdf'. PNG only by default. SVG and PDF are off unless this list asks for them -- add them here and nothing else changes, because one drawing produces every format and they cannot disagree. Written as a JSON list in the spreadsheet. To turn all three on: ["svg", "png", "pdf"]. A plain comma-separated list is also accepted, so svg, png, pdf typed straight into the cell works too. SAFE TO CHANGE: yes. PNG for anything that will not take a vector, SVG for the web and for editing, PDF for documents and printing.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>figures.formats</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>["png"]</t>
-        </is>
+          <t>figures.png</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Where figures are written, relative to the project root. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.svg</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raster resolution for PNG, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size. 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be above zero.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>200</v>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Colour scheme baked into the output: 'light' or 'dark'. The figures used to carry a `prefers-color-scheme` rule and switch by themselves. A PNG or PDF cannot, so the choice is made at render time. SAFE TO CHANGE: yes.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>figures.theme</t>
+          <t>figures.out_dir</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>figures</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>dpi</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Whether plot_flows draws one Sankey per element in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- turn it off to get the total only.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D12" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -491,17 +491,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>draw_flows</t>
+          <t>draw_structure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DRAW THE SANKEY FIGURES AS PART OF A RUN. These show how much mass goes where, in total and per element. SAFE TO CHANGE: yes. Set to False to solve without drawing anything.</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>run.draw_flows</t>
+          <t>run.draw_structure</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -511,57 +511,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>draw_structure</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALSO DRAW THE STRUCTURE DIAGRAM ON EVERY RUN. This shows how the flows connect and the transfer coefficients behind each arrow. Off by default because the structure only changes when the TC table changes, while the Sankeys change with every result. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run.draw_structure</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.pdf</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -571,104 +571,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>200</v>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>element_figures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>element_figures</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -491,37 +491,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>draw_structure</t>
+          <t>expected_unit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
+          <t>THE MASS UNIT THIS PROJECT WORKS IN. The model itself is unit-agnostic: it multiplies fractions, so it never looks at the unit. That is exactly why a wrong one is dangerous -- nothing downstream would notice. Every inflow row is checked against this, and a run stops if inputs.csv mixes two units in one file. Worth knowing: the upstream pipeline (04_02) delivers inflows in kt, and everything in this repository is written in Mg. That is a factor of 1000. Set this to whatever the inflow data actually is, and convert the data -- do not change this to silence a warning. SAFE TO CHANGE: yes, but only together with the data itself.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>run.draw_structure</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
+          <t>run.expected_unit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>draw_structure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>run.draw_structure</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -531,37 +533,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -571,84 +573,104 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>200</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D12" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -469,81 +469,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHICH OF THE TWO ENGINES SOLVES THE SYSTEM: 'optimized' or 'LA'. SAFE TO CHANGE: yes, but read this first. The two engines disagree beyond the basic_test case -- seven documented differences, several of which change results silently (documentation/DEFECTS.md section 2). 'optimized' is the default because it is what this project has always run, NOT because it is the more correct of the two.</t>
+          <t>WHICH SCENARIO TO RUN.  Blank when the data has no scenario dimension, which is the case for every data folder in this repository today.  ONE RUN IS ONE SCENARIO, across all its years. Scenarios are independent here -- this model is pure flow-through, with no stock carried between runs -- so nothing is gained by solving several at once, and under the Monte Carlo it costs: the memory budget is already the binding constraint (DESIGN_monte_carlo.md section 2). Separate runs also means five scenarios on five cores, and a failure that loses one rather than all.  Comparing scenarios is ANALYSIS, done afterwards on the output files. The model produces one scenario's numbers and stops there.  If the data holds scenarios and this is left blank, the run stops and lists what it found rather than guessing. SAFE TO CHANGE: yes -- it must name a scenario present in inputs.csv.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>run.engine</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>optimized</t>
-        </is>
-      </c>
+          <t>run.scenario</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>expected_unit</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THE MASS UNIT THIS PROJECT WORKS IN. The model itself is unit-agnostic: it multiplies fractions, so it never looks at the unit. That is exactly why a wrong one is dangerous -- nothing downstream would notice. Every inflow row is checked against this, and a run stops if inputs.csv mixes two units in one file. Worth knowing: the upstream pipeline (04_02) delivers inflows in kt, and everything in this repository is written in Mg. That is a factor of 1000. Set this to whatever the inflow data actually is, and convert the data -- do not change this to silence a warning. SAFE TO CHANGE: yes, but only together with the data itself.</t>
+          <t>WHICH OF THE TWO ENGINES SOLVES THE SYSTEM: 'optimized' or 'LA'. SAFE TO CHANGE: yes, but read this first. The two engines disagree beyond the basic_test case -- seven documented differences, several of which change results silently (documentation/DEFECTS.md section 2). 'optimized' is the default because it is what this project has always run, NOT because it is the more correct of the two.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>run.expected_unit</t>
+          <t>run.engine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mg</t>
+          <t>optimized</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>draw_structure</t>
+          <t>expected_unit</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
+          <t>THE MASS UNIT THIS PROJECT WORKS IN. The model itself is unit-agnostic: it multiplies fractions, so it never looks at the unit. That is exactly why a wrong one is dangerous -- nothing downstream would notice. Every inflow row is checked against this, and a run stops if inputs.csv mixes two units in one file. Worth knowing: the upstream pipeline (04_02) delivers inflows in kt, and everything in this repository is written in Mg. That is a factor of 1000. Set this to whatever the inflow data actually is, and convert the data -- do not change this to silence a warning. SAFE TO CHANGE: yes, but only together with the data itself.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run.draw_structure</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
+          <t>run.expected_unit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>draw_structure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>run.draw_structure</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -553,37 +551,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -593,84 +591,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>200</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D13" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -487,81 +487,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>years</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WHICH OF THE TWO ENGINES SOLVES THE SYSTEM: 'optimized' or 'LA'. SAFE TO CHANGE: yes, but read this first. The two engines disagree beyond the basic_test case -- seven documented differences, several of which change results silently (documentation/DEFECTS.md section 2). 'optimized' is the default because it is what this project has always run, NOT because it is the more correct of the two.</t>
+          <t>WHICH YEARS TO RUN.  Blank means every year the data holds.  ''               every year in inputs.csv '2030'           that one year '2030-2050'      that range, both ends included, every year in it '2030-2050,10'   that range, every 10th year: 2030, 2040, 2050 ',10'            every 10th year of the whole data  Real inflow data is annual -- the upstream arrays run 1975 to 2070 -- so a step is usually what you want rather than the full trajectory. It keeps the shape of the curve while cutting its size. The step counts by year value, not by row, so a gap in the data does not shift everything after it.  Several years in one run is normal, unlike scenarios which are one per run. Years are independent here too, but a result usually wants the trajectory rather than a point.  It matters for the Monte Carlo: 200,000 draws x 96 years is the memory problem in DESIGN_monte_carlo.md section 2, and the year axis is the most direct lever on it. SAFE TO CHANGE: yes -- it must match at least one year present in the data.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>run.engine</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>optimized</t>
-        </is>
-      </c>
+          <t>run.years</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>expected_unit</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THE MASS UNIT THIS PROJECT WORKS IN. The model itself is unit-agnostic: it multiplies fractions, so it never looks at the unit. That is exactly why a wrong one is dangerous -- nothing downstream would notice. Every inflow row is checked against this, and a run stops if inputs.csv mixes two units in one file. Worth knowing: the upstream pipeline (04_02) delivers inflows in kt, and everything in this repository is written in Mg. That is a factor of 1000. Set this to whatever the inflow data actually is, and convert the data -- do not change this to silence a warning. SAFE TO CHANGE: yes, but only together with the data itself.</t>
+          <t>WHICH OF THE TWO ENGINES SOLVES THE SYSTEM: 'optimized' or 'LA'. SAFE TO CHANGE: yes, but read this first. The two engines disagree beyond the basic_test case -- seven documented differences, several of which change results silently (documentation/DEFECTS.md section 2). 'optimized' is the default because it is what this project has always run, NOT because it is the more correct of the two.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run.expected_unit</t>
+          <t>run.engine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mg</t>
+          <t>optimized</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>draw_structure</t>
+          <t>expected_unit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
+          <t>THE MASS UNIT THIS PROJECT WORKS IN. The model itself is unit-agnostic: it multiplies fractions, so it never looks at the unit. That is exactly why a wrong one is dangerous -- nothing downstream would notice. Every inflow row is checked against this, and a run stops if inputs.csv mixes two units in one file. Worth knowing: the upstream pipeline (04_02) delivers inflows in kt, and everything in this repository is written in Mg. That is a factor of 1000. Set this to whatever the inflow data actually is, and convert the data -- do not change this to silence a warning. SAFE TO CHANGE: yes, but only together with the data itself.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run.draw_structure</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
+          <t>run.expected_unit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>draw_structure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>run.draw_structure</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -571,37 +569,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -611,84 +609,104 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>200</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D14" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -569,144 +569,208 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>upstream_root</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>WHERE THE UPSTREAM PROJECT IS, as a path from this project's root. The two repositories sit side by side, so the default works on any machine that has both checked out, without hard-coding a home directory. Written relative rather than absolute deliberately: the absolute path differs between the two Macs this project is worked on, and did so again when the folder moved into iCloud. SAFE TO CHANGE: yes -- it must point at the RAWCLICStockAndFlow checkout.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>figures.png</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
+          <t>data.upstream_root</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>../RAWCLICStockAndFlow</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>inflow_draws_dir</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WHERE THE PER-ELEMENT INFLOW DRAWS ARE, under `upstream_root`. One `.npy` per element per flow, each of shape (draws, years), in kt. The scenario named in `run.scenario` is appended to this path.  THIS DOES NOT EXIST YET, and that is the current blocker. Stage 04_02 of the upstream pipeline computes exactly these numbers -- vehicles per year times grams per vehicle, multiplied draw by draw so both uncertainties carry through -- but it only persists a *summary* pickle and its figures. The per-draw element arrays are discarded when it finishes.  The fix belongs upstream, not here: 04_02 gains a step that writes them. Recomputing them in this project would mean duplicating 04_02's segment splitting and draw pairing, and that pipeline's own header records three separate occasions where a stage reconstructed another stage's numbers and diverged silently. Read the real draws; do not re-derive them. SAFE TO CHANGE: yes -- it must name the folder 04_02 writes them to.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>figures.svg</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
+          <t>data.inflow_draws_dir</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>data/processed/element_draws</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>draws</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>HOW MANY OF THE DRAWS TO USE.  The upstream arrays hold 200,000. Lower this while developing: the memory arithmetic in DESIGN_monte_carlo.md section 2 is unforgiving at full width, and a few thousand draws is enough to see whether the machinery is correct. Raise it for a result that will be reported. Draws are taken from the front of the array, never sampled at random, so that a run at 5,000 is a strict prefix of a run at 200,000 and the two can be compared directly. SAFE TO CHANGE: yes. A whole number above zero, at most what the arrays hold.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
+          <t>data.draws</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>200000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.png</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>200</v>
+          <t>figures.svg</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>out_dir</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dpi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D14" t="b">
+      <c r="D17" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -627,23 +627,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>200000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>monte_carlo.enabled</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -653,124 +653,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>figures.svg</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
+          <t>monte_carlo.seed</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>chunk</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
+          <t>monte_carlo.chunk</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.png</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>200</v>
+          <t>figures.svg</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>out_dir</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dpi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D17" t="b">
+      <c r="D20" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -527,22 +527,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>expected_unit</t>
+          <t>working_unit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THE MASS UNIT THIS PROJECT WORKS IN. The model itself is unit-agnostic: it multiplies fractions, so it never looks at the unit. That is exactly why a wrong one is dangerous -- nothing downstream would notice. Every inflow row is checked against this, and a run stops if inputs.csv mixes two units in one file. Worth knowing: the upstream pipeline (04_02) delivers inflows in kt, and everything in this repository is written in Mg. That is a factor of 1000. Set this to whatever the inflow data actually is, and convert the data -- do not change this to silence a warning. SAFE TO CHANGE: yes, but only together with the data itself.</t>
+          <t>THE MASS UNIT THIS PROJECT WORKS IN. Every inflow is converted into this on load, from whatever its own file declares in the 'Unit' column, and every number the model writes is in it.  This used to be a check rather than a conversion: a file in another unit was reported and left alone, and converting it was a manual step. That is a poor arrangement when three units are genuinely in play -- the data folders here are written in Mg, the upstream pipeline delivers kt, and results are wanted in kg -- because the manual step can be forgotten and forgetting it is invisible. The model multiplies fractions, so a factor of 1000 leaves every ratio in the output looking perfectly reasonable.  Data files are NOT edited to match this. They keep saying what they are; this says what the answer should be in.  Worth knowing: no single unit suits both ends of this model. A year's collected fleet is around 500 kt and the gold in it is a few tonnes -- 500,000,000 kg against 3,000 kg. Figures therefore choose their own display unit per panel (src/units.py, scale_for); this setting governs the arithmetic and the output files. SAFE TO CHANGE: yes. Any unit in MASS_UNITS in src/units.py.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run.expected_unit</t>
+          <t>run.working_unit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mg</t>
+          <t>kg</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/template</t>
+          <t>data_folder/bev_electronics</t>
         </is>
       </c>
     </row>
@@ -633,204 +633,290 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>upstream_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
+          <t>WHICH UPSTREAM FLOW IS THE INFLOW TO RECOVERY. Upstream reports three: what entered the fleet, what left it, and what was collected for recycling. Recovery starts from what was collected -- the other two are the fleet's own story and are not handed to a recycler. SAFE TO CHANGE: yes. One of 'collected', 'outflow', 'inflow'.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>monte_carlo.enabled</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
+          <t>data.upstream_flow</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>import_year</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
+          <t>WHICH YEAR TO IMPORT. Must be one of the years upstream exported -- see bev_electronics_element_draws_years in the RAWCLICStockAndFlow settings. One year at a time is the normal way to work here: a recovery result is reported for a year, and the memory cost is linear in how many are held. `run.years` then selects within whatever the case folder holds. SAFE TO CHANGE: yes, together with the upstream export.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>monte_carlo.seed</t>
+          <t>data.import_year</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>chunk</t>
+          <t>import_case</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
+          <t>WHERE import_upstream.py WRITES THE CASE FOLDER, under data_folder/. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>monte_carlo.chunk</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>20000</v>
+          <t>data.import_case</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bev_electronics</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>import_domains</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>WHICH ELECTRONICS DOMAINS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>figures.png</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
+          <t>data.import_domains</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>monte_carlo.enabled</t>
         </is>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
+          <t>monte_carlo.seed</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>chunk</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>monte_carlo.chunk</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>200</v>
+          <t>figures.png</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.svg</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>out_dir</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dpi</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D20" t="b">
+      <c r="D24" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Wiring", "Motors"]</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHICH CASE THE MODEL RUNS. A folder holding an `input_data/` with the three CSV files: inputs.csv, composition.csv and TCs.csv. The path is written from the project root. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. To see which folders qualify, run:  ./.venv/bin/python 01_run_model.py --list</t>
+          <t>WHICH CASE THE MODEL RUNS. A folder holding an `input_data/` with the three CSV files: inputs.csv, composition.csv and TCs.csv. The path is written from the project root. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. To see which folders qualify, run:  ./.venv/bin/python 03_run_model.py --list</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,7 +500,11 @@
           <t>run.years</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2030-2050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -554,7 +558,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python plot_structure.py</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python tools/plot_structure.py</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="11">

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -777,63 +777,63 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>memory_budget_gb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open. SAFE TO CHANGE: yes. A number above zero.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>figures.png</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
+          <t>monte_carlo.memory_budget_gb</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -843,84 +843,104 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>200</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D24" t="b">
+      <c r="D25" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHICH CASE THE MODEL RUNS. A folder holding an `input_data/` with the three CSV files: inputs.csv, composition.csv and TCs.csv. The path is written from the project root. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. To see which folders qualify, run:  ./.venv/bin/python 03_run_model.py --list</t>
+          <t>WHICH CASE THE MODEL RUNS. A folder holding an `input_data/` with the three CSV files: inputs.csv, composition.csv and TCs.csv. The path is written from the project root. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. To see which folders qualify, run:  ./.venv/bin/python 02_run_model.py --list</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -701,119 +701,127 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>import_domains</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WHICH ELECTRONICS DOMAINS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
+          <t>WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>data.import_domains</t>
+          <t>data.product</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>["Wiring", "Motors"]</t>
+          <t>BEV</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>inflow_flow_id</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
+          <t>WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>monte_carlo.enabled</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
+          <t>data.inflow_flow_id</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>material_suffix</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
+          <t>WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. Upstream has no material resolution -- it goes straight from a group to the elements in it -- so each group gets exactly one material named after it. The layer is carried for the model's sake and means nothing. SAFE TO CHANGE: yes -- it is a label.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>monte_carlo.seed</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
+          <t>data.material_suffix</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>_mixed</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>chunk</t>
+          <t>group_marker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
+          <t>HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>monte_carlo.chunk</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
+          <t>data.group_marker</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>__domain__</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>memory_budget_gb</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open. SAFE TO CHANGE: yes. A number above zero.</t>
+          <t>WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>monte_carlo.memory_budget_gb</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
+          <t>data.groups</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>["Wiring", "Motors"]</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>monte_carlo.enabled</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -823,124 +831,204 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>figures.svg</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
+          <t>monte_carlo.seed</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>chunk</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
+          <t>monte_carlo.chunk</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>memory_budget_gb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open. SAFE TO CHANGE: yes. A number above zero.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>monte_carlo.memory_budget_gb</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>200</v>
+          <t>figures.png</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.svg</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>out_dir</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dpi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D25" t="b">
+      <c r="D29" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHERE THE PER-ELEMENT INFLOW DRAWS ARE, under `upstream_root`. One `.npy` per element per flow, each of shape (draws, years), in kt. The scenario named in `run.scenario` is appended to this path.  THIS DOES NOT EXIST YET, and that is the current blocker. Stage 04_02 of the upstream pipeline computes exactly these numbers -- vehicles per year times grams per vehicle, multiplied draw by draw so both uncertainties carry through -- but it only persists a *summary* pickle and its figures. The per-draw element arrays are discarded when it finishes.  The fix belongs upstream, not here: 04_02 gains a step that writes them. Recomputing them in this project would mean duplicating 04_02's segment splitting and draw pairing, and that pipeline's own header records three separate occasions where a stage reconstructed another stage's numbers and diverged silently. Read the real draws; do not re-derive them. SAFE TO CHANGE: yes -- it must name the folder 04_02 writes them to.</t>
+          <t>BY CASE (`upstream_dir` in source.csv). WHERE THE PER-CHILD INFLOW DRAWS ARE, under `upstream_root`. One `.npy` per child per flow, each of shape (draws, years), in kt. The scenario named in `run.scenario` is appended to this path.  These are written by a year-sliced export step in the upstream stage -- built for 04_02, to be mirrored for the others. Recomputing them here would mean duplicating that stage's segment splitting and draw pairing, and that pipeline's own header records three separate occasions where a stage reconstructed another stage's numbers and diverged silently. Read the real draws; do not re-derive them. SAFE TO CHANGE: yes -- but prefer saying it in the case's source.csv.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHICH UPSTREAM FLOW IS THE INFLOW TO RECOVERY. Upstream reports three: what entered the fleet, what left it, and what was collected for recycling. Recovery starts from what was collected -- the other two are the fleet's own story and are not handed to a recycler. SAFE TO CHANGE: yes. One of 'collected', 'outflow', 'inflow'.</t>
+          <t>BY CASE (`flow` in source.csv). WHICH UPSTREAM FLOW IS THE INFLOW TO RECOVERY. Upstream reports three: what entered the fleet, what left it, and what was collected for recycling. Recovery starts from what was collected -- the other two are the fleet's own story and are not handed to a recycler. SAFE TO CHANGE: yes. One of 'collected', 'outflow', 'inflow'.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
+          <t>BY CASE (`product` in source.csv). WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
+          <t>BY CASE (`inflow_flow_id` in source.csv). WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. Upstream has no material resolution -- it goes straight from a group to the elements in it -- so each group gets exactly one material named after it. The layer is carried for the model's sake and means nothing. SAFE TO CHANGE: yes -- it is a label.</t>
+          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. Upstream has no material resolution -- it goes straight from a group to the elements in it -- so each group gets exactly one material named after it. The layer is carried for the model's sake and means nothing. SAFE TO CHANGE: yes -- it is a label.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
+          <t>BY CASE (`group_marker` in source.csv). HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
+          <t>BY CASE (`groups` in source.csv, semicolon-separated). WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="11">

--- a/params.xlsx
+++ b/params.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="11">

--- a/params.xlsx
+++ b/params.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHICH CASE THE MODEL RUNS. A folder holding an `input_data/` with the three CSV files: inputs.csv, composition.csv and TCs.csv. The path is written from the project root. SAFE TO CHANGE: yes -- this is the setting that changes on most runs. To see which folders qualify, run:  ./.venv/bin/python 02_run_model.py --list</t>
+          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on RUN.py.  'data_folder/bev_electronics'        04_02  electronics in BEVs, resolved to ELEMENTS 'data_folder/carcomposition_mockup'  04_01  whole cars, five drivetrains, resolved to MATERIALS  ONE AT A TIME. They are different studies -- different networks, different coefficients, different layers -- and a result is reported for one of them, never for both together.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** A folder holding an `input_data/`, written from the project root. RUN.py lists the folders that qualify if this one does not exist. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on RUN.py.  'data_folder/bev_electronics'        04_02  electronics in BEVs, resolved to ELEMENTS 'data_folder/carcomposition_mockup'  04_01  whole cars, five drivetrains, resolved to MATERIALS  ONE AT A TIME. They are different studies -- different networks, different coefficients, different layers -- and a result is reported for one of them, never for both together.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** A folder holding an `input_data/`, written from the project root. RUN.py lists the folders that qualify if this one does not exist. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
+          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics'        04_02  electronics in BEVs, resolved to ELEMENTS 'data_folder/carcomposition_mockup'  04_01  whole cars, five drivetrains, resolved to MATERIALS  ONE AT A TIME. They are different studies -- different networks, different coefficients, different layers -- and a result is reported for one of them, never for both together.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** A folder holding an `input_data/`, written from the project root. `02_run_model.py --list` prints the folders that qualify. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -659,376 +659,334 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>import_year</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WHICH YEAR TO IMPORT. Must be one of the years upstream exported -- see bev_electronics_element_draws_years in the RAWCLICStockAndFlow settings. One year at a time is the normal way to work here: a recovery result is reported for a year, and the memory cost is linear in how many are held. `run.years` then selects within whatever the case folder holds. SAFE TO CHANGE: yes, together with the upstream export.</t>
+          <t>BY CASE (`product` in source.csv). WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>data.import_year</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2040</v>
+          <t>data.product</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>import_case</t>
+          <t>inflow_flow_id</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WHERE import_upstream.py WRITES THE CASE FOLDER, under data_folder/. SAFE TO CHANGE: yes.</t>
+          <t>BY CASE (`inflow_flow_id` in source.csv). WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>data.import_case</t>
+          <t>data.inflow_flow_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bev_electronics</t>
+          <t>F_collected</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>material_suffix</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BY CASE (`product` in source.csv). WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
+          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. Upstream has no material resolution -- it goes straight from a group to the elements in it -- so each group gets exactly one material named after it. The layer is carried for the model's sake and means nothing. SAFE TO CHANGE: yes -- it is a label.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>data.product</t>
+          <t>data.material_suffix</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>_mixed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inflow_flow_id</t>
+          <t>group_marker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BY CASE (`inflow_flow_id` in source.csv). WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
+          <t>BY CASE (`group_marker` in source.csv). HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>data.inflow_flow_id</t>
+          <t>data.group_marker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>__domain__</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>material_suffix</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. Upstream has no material resolution -- it goes straight from a group to the elements in it -- so each group gets exactly one material named after it. The layer is carried for the model's sake and means nothing. SAFE TO CHANGE: yes -- it is a label.</t>
+          <t>BY CASE (`groups` in source.csv, semicolon-separated). WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>data.material_suffix</t>
+          <t>data.groups</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>_mixed</t>
+          <t>["Wiring", "Motors"]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>group_marker</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BY CASE (`group_marker` in source.csv). HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
+          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>data.group_marker</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>__domain__</t>
-        </is>
+          <t>monte_carlo.enabled</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BY CASE (`groups` in source.csv, semicolon-separated). WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
+          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>data.groups</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>["Wiring", "Motors"]</t>
-        </is>
+          <t>monte_carlo.seed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>chunk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
+          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>monte_carlo.enabled</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
+          <t>monte_carlo.chunk</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>memory_budget_gb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
+          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open. SAFE TO CHANGE: yes. A number above zero.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>monte_carlo.seed</t>
+          <t>monte_carlo.memory_budget_gb</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chunk</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>monte_carlo.chunk</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
+          <t>figures.png</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>memory_budget_gb</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open. SAFE TO CHANGE: yes. A number above zero.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>monte_carlo.memory_budget_gb</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
+          <t>figures.svg</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>figures.png</t>
+          <t>figures.pdf</t>
         </is>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>figures.svg</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>0</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
+          <t>figures.theme</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>figures</t>
+          <t>light</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>element_figures</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>theme</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>element_figures</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D29" t="b">
+      <c r="D27" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -849,57 +849,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>sum_to_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>HOW A GROUP WITH NO `is_residual` ROW IS MADE TO SUM TO 1.  'normalise'   divide the group by its own sum. Always works, needs nothing added to the table, and shifts every marginal off the triangular it was drawn from. 'condition'   keep every row's own measurement: draw them all, take the widest as determined by the rest, weight each draw by that row's own density at the value it was forced to, and resample. This is what "sum to 1" means probabilistically -- the product of the measured densities, restricted to the draws that do sum to 1.  Use 'condition' when every row carries a measured range and you want all of them used. It also makes a contradiction visible: ranges that cannot all be true collapse the effective sample size, which stage 03 reports, instead of being silently absorbed.  Groups that DO name a residual row are unaffected. That row has no measurement of its own -- its bounds must be blank -- so there is nothing to condition on, and for a two-row group the residual rule is exact.  SAFE TO CHANGE: yes, but it changes the numbers for any group where every row has a range. It is not a tuning knob; it is a modelling choice.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>figures.png</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
+          <t>monte_carlo.sum_to_one</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>normalise</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -909,84 +911,104 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>200</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>element_figures</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>figures.element_figures</t>
         </is>
       </c>
-      <c r="D27" t="b">
+      <c r="D28" t="b">
         <v>1</v>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOW A GROUP WITH NO `is_residual` ROW IS MADE TO SUM TO 1.  'normalise'   divide the group by its own sum. Always works, needs nothing added to the table, and shifts every marginal off the triangular it was drawn from. 'condition'   keep every row's own measurement: draw them all, take the widest as determined by the rest, weight each draw by that row's own density at the value it was forced to, and resample. This is what "sum to 1" means probabilistically -- the product of the measured densities, restricted to the draws that do sum to 1.  Use 'condition' when every row carries a measured range and you want all of them used. It also makes a contradiction visible: ranges that cannot all be true collapse the effective sample size, which stage 03 reports, instead of being silently absorbed.  Groups that DO name a residual row are unaffected. That row has no measurement of its own -- its bounds must be blank -- so there is nothing to condition on, and for a two-row group the residual rule is exact.  SAFE TO CHANGE: yes, but it changes the numbers for any group where every row has a range. It is not a tuning knob; it is a modelling choice.</t>
+          <t>HOW A GROUP WITH NO `is_residual` ROW IS MADE TO SUM TO 1.  'normalise'   divide the group by its own sum. Always works, needs nothing added to the table, and shifts every marginal off the triangular it was drawn from. 'condition'   keep every row's own measurement: draw them all, take the widest as determined by the rest, weight each draw by that row's own density at the value it was forced to, and resample. This is what "sum to 1" means probabilistically -- the product of the measured densities, restricted to the draws that do sum to 1.  Use 'condition' when every row carries a measured range and you want all of them used. It also makes a contradiction visible: ranges that cannot all be true collapse the effective sample size, which stage 03 reports, instead of being silently absorbed.  Groups that DO name a residual row are unaffected. That row has no measurement of its own -- its bounds must be blank -- so there is nothing to condition on, and for a two-row group the residual rule is exact.  SAFE TO CHANGE: yes, but it changes the numbers for any group where every row has a range. It is not a tuning knob; it is a modelling choice.  'normalise' is kept for two reasons and no others: reproducing a result computed before conditioning existed, and getting a number out of a group whose ranges contradict each other, which conditioning refuses. Note what the second one means -- normalising a contradictory group does not resolve the contradiction, it hides it.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>normalise</t>
+          <t>condition</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RUN THE MONTE CARLO AT ALL. Off by default: a data folder whose TCs.csv has no value_min / value_max columns has nothing to sample, and every draw would return the same number. Stage 03 says so plainly rather than producing a flat histogram. SAFE TO CHANGE: yes.</t>
+          <t>RUN THE MONTE CARLO AT ALL. On, because both cases carry value_min and value_max and the spread is the point of running them. A case whose TC table has neither column has nothing to sample -- every draw would return the same number -- and stage 03 says so plainly rather than producing a flat histogram, so leaving this on costs nothing even then.  (This comment used to read "off by default" while the value was True. Found by the documentation sweep on 2026-08-26.) SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/bev_electronics</t>
+          <t>data_folder/bev_electronics_all_measured</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/bev_electronics_all_measured</t>
+          <t>data_folder/bev_electronics</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. Upstream has no material resolution -- it goes straight from a group to the elements in it -- so each group gets exactly one material named after it. The layer is carried for the model's sake and means nothing. SAFE TO CHANGE: yes -- it is a label.</t>
+          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. It holds what the upstream file names do NOT resolve into a material. A file named &lt;element&gt;__&lt;material&gt;__&lt;group&gt; puts its material at Layer 3 in its own right; where there is no such file the element's material is unknown, and the placeholder is where it sits. An export with none of them gives one placeholder per group holding the whole of it, which is what every case read before 2026-08-31. See CASES.md, `child_layer`. SAFE TO CHANGE: yes -- it is a label.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/bev_electronics</t>
+          <t>data_folder/bev_electronics_metals</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/bev_electronics_metals</t>
+          <t>data_folder/bev_electronics_wiring</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics'        04_02  electronics in BEVs, resolved to ELEMENTS 'data_folder/carcomposition_mockup'  04_01  whole cars, five drivetrains, resolved to MATERIALS  ONE AT A TIME. They are different studies -- different networks, different coefficients, different layers -- and a result is reported for one of them, never for both together.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** A folder holding an `input_data/`, written from the project root. `02_run_model.py --list` prints the folders that qualify. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
+          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data_folder/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data_folder/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS  ONE AT A TIME. They are different studies -- different networks, different coefficients, different layers -- and a result is reported for one of them, never for both together.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** A folder holding an `input_data/`, written from the project root. `02_run_model.py --list` prints the folders that qualify. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2030-2050</t>
+          <t>2020-2070, 5</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open. SAFE TO CHANGE: yes. A number above zero.</t>
+          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open; 8 suits the 32 GB machine this is developed on, and is what the boards case needs -- 1,661 rows x 200,000 draws is 2.7 GB of result and about 4.5 GB in all, which 4 refused. SAFE TO CHANGE: yes. A number above zero.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1012,6 +1012,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on routes.png, fate.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>figures.resources</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/params.xlsx
+++ b/params.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["copper"]</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/bev_electronics_wiring</t>
+          <t>data_folder/bev_electronics_boards</t>
         </is>
       </c>
     </row>
